--- a/data/raw/inventory/Week 33/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 33/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -1146,10 +1146,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2510,10 +2510,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>12</v>
@@ -3077,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3130,10 +3130,10 @@
         <v>13</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -3254,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
         <v>3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -3325,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>3</v>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -4680,10 +4680,10 @@
         <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -5052,10 +5052,10 @@
         <v>5</v>
       </c>
       <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
         <v>2</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -5176,10 +5176,10 @@
         <v>7</v>
       </c>
       <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
         <v>1</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -5300,10 +5300,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
         <v>1</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -5548,10 +5548,10 @@
         <v>2</v>
       </c>
       <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
         <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -7284,10 +7284,10 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -7408,10 +7408,10 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
         <v>1</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -7532,10 +7532,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
         <v>2</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -7656,10 +7656,10 @@
         <v>3</v>
       </c>
       <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
         <v>1</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -7904,10 +7904,10 @@
         <v>6</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -8090,10 +8090,10 @@
         <v>195</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -8152,10 +8152,10 @@
         <v>17</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -8276,10 +8276,10 @@
         <v>11</v>
       </c>
       <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
         <v>1</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -8462,10 +8462,10 @@
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -8524,10 +8524,10 @@
         <v>2</v>
       </c>
       <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
         <v>1</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -9330,10 +9330,10 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
         <v>3</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F156" t="n">
         <v>19</v>
@@ -10083,10 +10083,10 @@
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K156" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
@@ -10136,10 +10136,10 @@
         <v>7</v>
       </c>
       <c r="G157" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F159" t="n">
         <v>5</v>
@@ -10269,10 +10269,10 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -10626,25 +10626,25 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F165" t="n">
         <v>5</v>
       </c>
       <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
         <v>2</v>
       </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
       <c r="I165" t="n">
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -10880,10 +10880,10 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -12616,10 +12616,10 @@
         <v>3</v>
       </c>
       <c r="G197" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -13298,10 +13298,10 @@
         <v>1</v>
       </c>
       <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
         <v>1</v>
-      </c>
-      <c r="H208" t="n">
-        <v>0</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -14349,19 +14349,19 @@
         <v>795</v>
       </c>
       <c r="F225" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G225" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
       </c>
       <c r="J225" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K225" t="n">
         <v>795</v>
@@ -14414,10 +14414,10 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -15220,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
         <v>2</v>
-      </c>
-      <c r="H239" t="n">
-        <v>0</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -16398,10 +16398,10 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
         <v>1</v>
-      </c>
-      <c r="H258" t="n">
-        <v>0</v>
       </c>
       <c r="I258" t="n">
         <v>0</v>
@@ -16640,7 +16640,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F262" t="n">
         <v>0</v>
@@ -16655,10 +16655,10 @@
         <v>0</v>
       </c>
       <c r="J262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K262" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L262" t="n">
         <v>1</v>
@@ -16702,7 +16702,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F263" t="n">
         <v>1</v>
@@ -16717,10 +16717,10 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K263" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L263" t="n">
         <v>3</v>
@@ -17080,10 +17080,10 @@
         <v>82</v>
       </c>
       <c r="G269" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I269" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F272" t="n">
         <v>170</v>
@@ -17275,10 +17275,10 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K272" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L272" t="n">
         <v>2</v>
@@ -17384,7 +17384,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F274" t="n">
         <v>16</v>
@@ -17399,10 +17399,10 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -17948,10 +17948,10 @@
         <v>4</v>
       </c>
       <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="n">
         <v>4</v>
-      </c>
-      <c r="H283" t="n">
-        <v>0</v>
       </c>
       <c r="I283" t="n">
         <v>0</v>
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F323" t="n">
         <v>0</v>
@@ -20437,10 +20437,10 @@
         <v>0</v>
       </c>
       <c r="J323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -20924,16 +20924,16 @@
         <v>732</v>
       </c>
       <c r="G331" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="I331" t="n">
         <v>0</v>
       </c>
       <c r="J331" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K331" t="n">
         <v>910</v>
@@ -20942,7 +20942,7 @@
         <v>5</v>
       </c>
       <c r="M331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N331" t="inlineStr">
         <is>
@@ -21110,10 +21110,10 @@
         <v>9</v>
       </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I334" t="n">
         <v>0</v>
@@ -21166,10 +21166,10 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F335" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G335" t="n">
         <v>0</v>
@@ -21181,10 +21181,10 @@
         <v>0</v>
       </c>
       <c r="J335" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K335" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L335" t="n">
         <v>4</v>
@@ -21730,10 +21730,10 @@
         <v>22</v>
       </c>
       <c r="G344" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H344" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I344" t="n">
         <v>0</v>
@@ -24272,10 +24272,10 @@
         <v>5</v>
       </c>
       <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="n">
         <v>1</v>
-      </c>
-      <c r="H385" t="n">
-        <v>0</v>
       </c>
       <c r="I385" t="n">
         <v>0</v>
@@ -24520,10 +24520,10 @@
         <v>4</v>
       </c>
       <c r="G389" t="n">
+        <v>0</v>
+      </c>
+      <c r="H389" t="n">
         <v>2</v>
-      </c>
-      <c r="H389" t="n">
-        <v>0</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
@@ -27124,10 +27124,10 @@
         <v>4</v>
       </c>
       <c r="G431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H431" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I431" t="n">
         <v>0</v>
@@ -28054,10 +28054,10 @@
         <v>4</v>
       </c>
       <c r="G446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H446" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I446" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>1</v>
       </c>
       <c r="G448" t="n">
+        <v>0</v>
+      </c>
+      <c r="H448" t="n">
         <v>1</v>
-      </c>
-      <c r="H448" t="n">
-        <v>0</v>
       </c>
       <c r="I448" t="n">
         <v>0</v>
@@ -28488,10 +28488,10 @@
         <v>0</v>
       </c>
       <c r="G453" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" t="n">
         <v>5</v>
-      </c>
-      <c r="H453" t="n">
-        <v>0</v>
       </c>
       <c r="I453" t="n">
         <v>0</v>
